--- a/Antonio_Database.xlsx
+++ b/Antonio_Database.xlsx
@@ -413,9 +413,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Order ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dynneal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Caesar Salad</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dynneal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Caesar Salad</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>250</v>
+      </c>
+      <c r="F3" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Antonio_Database.xlsx
+++ b/Antonio_Database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,26 +450,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dani</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>French Toast</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dynneal</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Caesar Salad</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
       <c r="E2" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -478,22 +478,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dynneal</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Caesar Salad</t>
+          <t>Carbonara</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>180</v>
+      </c>
+      <c r="F3" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chae</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Caramel Macchiato</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>250</v>
-      </c>
-      <c r="F3" t="n">
-        <v>250</v>
+      <c r="E4" t="n">
+        <v>135</v>
+      </c>
+      <c r="F4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Trina</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fries</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
